--- a/data/trans_orig/P34A_R-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P34A_R-Clase-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que no realiza actividad física en su tiempo libre en 2007</t>
+          <t>Población que no realiza actividad física en su tiempo libre en 2007 (tasa de respuesta: 98,45%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>142302</t>
+          <t>142312</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>183892</t>
+          <t>184169</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>30,3%</t>
+          <t>30,31%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>39,16%</t>
+          <t>39,22%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>93208</t>
+          <t>94224</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>126405</t>
+          <t>127767</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>31,08%</t>
+          <t>31,42%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>42,15%</t>
+          <t>42,61%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>247259</t>
+          <t>250987</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>299604</t>
+          <t>305476</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>32,13%</t>
+          <t>32,62%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>38,94%</t>
+          <t>39,7%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>285679</t>
+          <t>285402</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>327269</t>
+          <t>327259</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>60,84%</t>
+          <t>60,78%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>69,7%</t>
+          <t>69,69%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>173474</t>
+          <t>172112</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>206671</t>
+          <t>205655</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>57,85%</t>
+          <t>57,39%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>68,92%</t>
+          <t>68,58%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>469846</t>
+          <t>463974</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>522191</t>
+          <t>518463</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>61,06%</t>
+          <t>60,3%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>67,87%</t>
+          <t>67,38%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>90297</t>
+          <t>90968</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>125853</t>
+          <t>126967</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>25,02%</t>
+          <t>25,2%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>34,87%</t>
+          <t>35,17%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>137834</t>
+          <t>136031</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>175299</t>
+          <t>174443</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>37,92%</t>
+          <t>37,42%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>48,23%</t>
+          <t>47,99%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>237688</t>
+          <t>236754</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>289610</t>
+          <t>290651</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>32,81%</t>
+          <t>32,68%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>39,98%</t>
+          <t>40,12%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>235117</t>
+          <t>234003</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>270673</t>
+          <t>270002</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>65,13%</t>
+          <t>64,83%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>74,98%</t>
+          <t>74,8%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>188185</t>
+          <t>189041</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>225650</t>
+          <t>227453</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>51,77%</t>
+          <t>52,01%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>62,08%</t>
+          <t>62,58%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>434844</t>
+          <t>433803</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>486766</t>
+          <t>487700</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>60,02%</t>
+          <t>59,88%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>67,19%</t>
+          <t>67,32%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>225524</t>
+          <t>225365</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>274612</t>
+          <t>272134</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>41,94%</t>
+          <t>41,91%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>51,07%</t>
+          <t>50,61%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>64289</t>
+          <t>64567</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>89321</t>
+          <t>89938</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>39,04%</t>
+          <t>39,21%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>54,25%</t>
+          <t>54,62%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>299356</t>
+          <t>299517</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>353887</t>
+          <t>351953</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>42,62%</t>
+          <t>42,64%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>50,38%</t>
+          <t>50,11%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>263104</t>
+          <t>265582</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>312192</t>
+          <t>312351</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>48,93%</t>
+          <t>49,39%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>58,06%</t>
+          <t>58,09%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>75340</t>
+          <t>74723</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>100372</t>
+          <t>100094</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>45,75%</t>
+          <t>45,38%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>60,96%</t>
+          <t>60,79%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>348490</t>
+          <t>350424</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>403021</t>
+          <t>402860</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>49,62%</t>
+          <t>49,89%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>57,38%</t>
+          <t>57,36%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>534358</t>
+          <t>537300</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>605519</t>
+          <t>606314</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>43,92%</t>
+          <t>44,16%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>49,76%</t>
+          <t>49,83%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>309441</t>
+          <t>307051</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>361201</t>
+          <t>360463</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>43,78%</t>
+          <t>43,44%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>51,1%</t>
+          <t>51,0%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>868076</t>
+          <t>863633</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>951391</t>
+          <t>954337</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>45,13%</t>
+          <t>44,9%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>49,46%</t>
+          <t>49,61%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>611279</t>
+          <t>610484</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>682440</t>
+          <t>679498</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>50,24%</t>
+          <t>50,17%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>56,08%</t>
+          <t>55,84%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>345587</t>
+          <t>346325</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>397347</t>
+          <t>399737</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>48,9%</t>
+          <t>49,0%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>56,22%</t>
+          <t>56,56%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>972195</t>
+          <t>969249</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1055510</t>
+          <t>1059953</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>50,54%</t>
+          <t>50,39%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>54,87%</t>
+          <t>55,1%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>155273</t>
+          <t>155952</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>192743</t>
+          <t>194065</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>45,29%</t>
+          <t>45,49%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>56,22%</t>
+          <t>56,6%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>274544</t>
+          <t>276463</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>324361</t>
+          <t>325627</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>49,46%</t>
+          <t>49,8%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>58,43%</t>
+          <t>58,66%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>442727</t>
+          <t>441394</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>505884</t>
+          <t>503726</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>49,3%</t>
+          <t>49,16%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>56,34%</t>
+          <t>56,1%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>150110</t>
+          <t>148788</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>187580</t>
+          <t>186901</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>43,78%</t>
+          <t>43,4%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>54,71%</t>
+          <t>54,51%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>230747</t>
+          <t>229481</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>280564</t>
+          <t>278645</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>41,57%</t>
+          <t>41,34%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>50,54%</t>
+          <t>50,2%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>392077</t>
+          <t>394235</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>455234</t>
+          <t>456567</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>43,66%</t>
+          <t>43,9%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>50,7%</t>
+          <t>50,84%</t>
         </is>
       </c>
     </row>
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>42320</t>
+          <t>43502</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>69342</t>
+          <t>71598</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>14,23%</t>
+          <t>14,63%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>23,32%</t>
+          <t>24,08%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>519083</t>
+          <t>516174</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>589340</t>
+          <t>585323</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>42,28%</t>
+          <t>42,04%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>48,0%</t>
+          <t>47,67%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>571732</t>
+          <t>570101</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>647868</t>
+          <t>644370</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>37,49%</t>
+          <t>37,38%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>42,48%</t>
+          <t>42,25%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>227960</t>
+          <t>225704</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>254982</t>
+          <t>253800</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,12 +2576,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>76,68%</t>
+          <t>75,92%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>85,77%</t>
+          <t>85,37%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>638425</t>
+          <t>642442</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>708682</t>
+          <t>711591</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>52,0%</t>
+          <t>52,33%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>57,72%</t>
+          <t>57,96%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>877199</t>
+          <t>880697</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>953335</t>
+          <t>954966</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>57,52%</t>
+          <t>57,75%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>62,51%</t>
+          <t>62,62%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>1264721</t>
+          <t>1264464</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>1378501</t>
+          <t>1381625</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2811,7 +2811,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>42,74%</t>
+          <t>42,84%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>1472384</t>
+          <t>1475555</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>1591396</t>
+          <t>1589148</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>44,38%</t>
+          <t>44,48%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>47,97%</t>
+          <t>47,9%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>2779962</t>
+          <t>2769556</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>2937072</t>
+          <t>2929625</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>42,49%</t>
+          <t>42,33%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>44,89%</t>
+          <t>44,78%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>1846709</t>
+          <t>1843585</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>1960489</t>
+          <t>1960746</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,7 +2919,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>57,26%</t>
+          <t>57,16%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>1726290</t>
+          <t>1728538</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>1845302</t>
+          <t>1842131</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>52,03%</t>
+          <t>52,1%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>55,62%</t>
+          <t>55,52%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>3605824</t>
+          <t>3613271</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>3762934</t>
+          <t>3773340</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>55,11%</t>
+          <t>55,22%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>57,51%</t>
+          <t>57,67%</t>
         </is>
       </c>
     </row>
@@ -3173,7 +3173,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que no realiza actividad física en su tiempo libre en 2012</t>
+          <t>Población que no realiza actividad física en su tiempo libre en 2012 (tasa de respuesta: 99,95%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3368,12 +3368,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>54552</t>
+          <t>53725</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>86599</t>
+          <t>86688</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3383,12 +3383,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>12,48%</t>
+          <t>12,29%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>19,81%</t>
+          <t>19,83%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3403,12 +3403,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>53494</t>
+          <t>52108</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>83017</t>
+          <t>82216</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3418,12 +3418,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>17,01%</t>
+          <t>16,57%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>26,4%</t>
+          <t>26,15%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3438,12 +3438,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>114216</t>
+          <t>113504</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>158843</t>
+          <t>159970</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3453,12 +3453,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>15,2%</t>
+          <t>15,1%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>21,13%</t>
+          <t>21,28%</t>
         </is>
       </c>
     </row>
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>350612</t>
+          <t>350523</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>382659</t>
+          <t>383486</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3496,12 +3496,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>80,19%</t>
+          <t>80,17%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>87,52%</t>
+          <t>87,71%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3516,12 +3516,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>231437</t>
+          <t>232238</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>260960</t>
+          <t>262346</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3531,12 +3531,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>73,6%</t>
+          <t>73,85%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>82,99%</t>
+          <t>83,43%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3551,12 +3551,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>592822</t>
+          <t>591695</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>637449</t>
+          <t>638161</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3566,12 +3566,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>78,87%</t>
+          <t>78,72%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>84,8%</t>
+          <t>84,9%</t>
         </is>
       </c>
     </row>
@@ -3711,12 +3711,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>59890</t>
+          <t>60368</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>92912</t>
+          <t>94623</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3726,12 +3726,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>14,3%</t>
+          <t>14,41%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>22,19%</t>
+          <t>22,59%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3746,12 +3746,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>70170</t>
+          <t>71716</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>104355</t>
+          <t>105899</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3761,12 +3761,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>20,76%</t>
+          <t>21,22%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>30,87%</t>
+          <t>31,33%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3781,12 +3781,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>138282</t>
+          <t>136325</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>184862</t>
+          <t>185898</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3796,12 +3796,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>18,27%</t>
+          <t>18,01%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>24,43%</t>
+          <t>24,56%</t>
         </is>
       </c>
     </row>
@@ -3824,12 +3824,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>325885</t>
+          <t>324174</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>358907</t>
+          <t>358429</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3839,12 +3839,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>77,81%</t>
+          <t>77,41%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>85,7%</t>
+          <t>85,59%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3859,12 +3859,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>233656</t>
+          <t>232112</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>267841</t>
+          <t>266295</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3874,12 +3874,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>69,13%</t>
+          <t>68,67%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>79,24%</t>
+          <t>78,78%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3894,12 +3894,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>571946</t>
+          <t>570910</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>618526</t>
+          <t>620483</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3909,12 +3909,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>75,57%</t>
+          <t>75,44%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>81,73%</t>
+          <t>81,99%</t>
         </is>
       </c>
     </row>
@@ -4054,12 +4054,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>135854</t>
+          <t>138964</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>180706</t>
+          <t>183250</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4069,12 +4069,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>21,61%</t>
+          <t>22,11%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>28,75%</t>
+          <t>29,16%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4089,12 +4089,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>75436</t>
+          <t>77219</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>106099</t>
+          <t>107661</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4104,12 +4104,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>29,0%</t>
+          <t>29,68%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>40,79%</t>
+          <t>41,39%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4124,12 +4124,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>226962</t>
+          <t>221465</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>281455</t>
+          <t>279296</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4139,12 +4139,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>25,54%</t>
+          <t>24,92%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>31,67%</t>
+          <t>31,43%</t>
         </is>
       </c>
     </row>
@@ -4167,12 +4167,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>447812</t>
+          <t>445268</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>492664</t>
+          <t>489554</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4182,12 +4182,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>71,25%</t>
+          <t>70,84%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>78,39%</t>
+          <t>77,89%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4202,12 +4202,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>154030</t>
+          <t>152468</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>184693</t>
+          <t>182910</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4217,12 +4217,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>59,21%</t>
+          <t>58,61%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>71,0%</t>
+          <t>70,32%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4237,12 +4237,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>607192</t>
+          <t>609351</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>661685</t>
+          <t>667182</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4252,12 +4252,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>68,33%</t>
+          <t>68,57%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>74,46%</t>
+          <t>75,08%</t>
         </is>
       </c>
     </row>
@@ -4397,12 +4397,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>264837</t>
+          <t>264394</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>326681</t>
+          <t>324860</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4412,12 +4412,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>22,87%</t>
+          <t>22,83%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>28,21%</t>
+          <t>28,05%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4432,12 +4432,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>209094</t>
+          <t>210990</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>259188</t>
+          <t>262904</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4447,12 +4447,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>27,27%</t>
+          <t>27,52%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>33,81%</t>
+          <t>34,29%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4467,12 +4467,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>491813</t>
+          <t>491982</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>571594</t>
+          <t>574200</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4482,12 +4482,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>25,55%</t>
+          <t>25,56%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>29,7%</t>
+          <t>29,83%</t>
         </is>
       </c>
     </row>
@@ -4510,12 +4510,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>831467</t>
+          <t>833288</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>893311</t>
+          <t>893754</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4525,12 +4525,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>71,79%</t>
+          <t>71,95%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>77,13%</t>
+          <t>77,17%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4545,12 +4545,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>507469</t>
+          <t>503753</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>557563</t>
+          <t>555667</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>66,19%</t>
+          <t>65,71%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>72,73%</t>
+          <t>72,48%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4580,12 +4580,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1353212</t>
+          <t>1350606</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1432993</t>
+          <t>1432824</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4595,12 +4595,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>70,3%</t>
+          <t>70,17%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>74,45%</t>
+          <t>74,44%</t>
         </is>
       </c>
     </row>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>120886</t>
+          <t>125278</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>164241</t>
+          <t>165570</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4755,12 +4755,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>23,68%</t>
+          <t>24,54%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>32,17%</t>
+          <t>32,43%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>253578</t>
+          <t>254444</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>305373</t>
+          <t>307500</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4790,12 +4790,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>33,3%</t>
+          <t>33,41%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>40,1%</t>
+          <t>40,38%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>387289</t>
+          <t>389220</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>455184</t>
+          <t>457323</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>30,44%</t>
+          <t>30,6%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>35,78%</t>
+          <t>35,95%</t>
         </is>
       </c>
     </row>
@@ -4853,12 +4853,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>346355</t>
+          <t>345026</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>389710</t>
+          <t>385318</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4868,12 +4868,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>67,83%</t>
+          <t>67,57%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>76,32%</t>
+          <t>75,46%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4888,12 +4888,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>456149</t>
+          <t>454022</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>507944</t>
+          <t>507078</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4903,12 +4903,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>59,9%</t>
+          <t>59,62%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>66,7%</t>
+          <t>66,59%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4923,12 +4923,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>816934</t>
+          <t>814795</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>884829</t>
+          <t>882898</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4938,12 +4938,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>64,22%</t>
+          <t>64,05%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>69,56%</t>
+          <t>69,4%</t>
         </is>
       </c>
     </row>
@@ -5083,12 +5083,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>21247</t>
+          <t>21132</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>42572</t>
+          <t>41629</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>7,96%</t>
+          <t>7,92%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>15,95%</t>
+          <t>15,6%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>306659</t>
+          <t>305915</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>370109</t>
+          <t>365981</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>27,67%</t>
+          <t>27,6%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>33,4%</t>
+          <t>33,02%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>335445</t>
+          <t>336640</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>401026</t>
+          <t>403330</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>24,39%</t>
+          <t>24,48%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>29,16%</t>
+          <t>29,33%</t>
         </is>
       </c>
     </row>
@@ -5196,12 +5196,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>224310</t>
+          <t>225253</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>245635</t>
+          <t>245750</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5211,12 +5211,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>84,05%</t>
+          <t>84,4%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>92,04%</t>
+          <t>92,08%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5231,12 +5231,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>738145</t>
+          <t>742273</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>801595</t>
+          <t>802339</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5246,12 +5246,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>66,6%</t>
+          <t>66,98%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>72,33%</t>
+          <t>72,4%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5266,12 +5266,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>974110</t>
+          <t>971806</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1039691</t>
+          <t>1038496</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5281,12 +5281,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>70,84%</t>
+          <t>70,67%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>75,61%</t>
+          <t>75,52%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>713231</t>
+          <t>720172</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>818951</t>
+          <t>817726</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>20,85%</t>
+          <t>21,06%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>23,94%</t>
+          <t>23,91%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>1044707</t>
+          <t>1043274</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>1153673</t>
+          <t>1154818</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>29,44%</t>
+          <t>29,4%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>32,51%</t>
+          <t>32,54%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1790230</t>
+          <t>1790240</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1943122</t>
+          <t>1936669</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5516,7 +5516,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>27,88%</t>
+          <t>27,79%</t>
         </is>
       </c>
     </row>
@@ -5539,12 +5539,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>2601201</t>
+          <t>2602426</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>2706921</t>
+          <t>2699980</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5554,12 +5554,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>76,06%</t>
+          <t>76,09%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>79,15%</t>
+          <t>78,94%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5574,12 +5574,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>2395355</t>
+          <t>2394210</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>2504321</t>
+          <t>2505754</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5589,12 +5589,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>67,49%</t>
+          <t>67,46%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>70,56%</t>
+          <t>70,6%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5609,12 +5609,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>5026058</t>
+          <t>5032511</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>5178950</t>
+          <t>5178940</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5624,7 +5624,7 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>72,12%</t>
+          <t>72,21%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
@@ -5808,7 +5808,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que no realiza actividad física en su tiempo libre en 2016</t>
+          <t>Población que no realiza actividad física en su tiempo libre en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6003,12 +6003,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>90669</t>
+          <t>90840</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>126855</t>
+          <t>127857</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6018,12 +6018,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>21,13%</t>
+          <t>21,17%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>29,56%</t>
+          <t>29,8%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6038,12 +6038,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>81494</t>
+          <t>81061</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>114739</t>
+          <t>114874</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6053,12 +6053,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>23,48%</t>
+          <t>23,36%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>33,06%</t>
+          <t>33,1%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6073,12 +6073,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>182625</t>
+          <t>183991</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>231025</t>
+          <t>231684</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6088,12 +6088,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>23,53%</t>
+          <t>23,71%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>29,77%</t>
+          <t>29,85%</t>
         </is>
       </c>
     </row>
@@ -6116,12 +6116,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>302237</t>
+          <t>301235</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>338423</t>
+          <t>338252</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6131,12 +6131,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>70,44%</t>
+          <t>70,2%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>78,87%</t>
+          <t>78,83%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6151,12 +6151,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>232316</t>
+          <t>232181</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>265561</t>
+          <t>265994</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6166,12 +6166,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>66,94%</t>
+          <t>66,9%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>76,52%</t>
+          <t>76,64%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6186,12 +6186,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>545122</t>
+          <t>544463</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>593522</t>
+          <t>592156</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6201,12 +6201,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>70,23%</t>
+          <t>70,15%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>76,47%</t>
+          <t>76,29%</t>
         </is>
       </c>
     </row>
@@ -6346,12 +6346,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>80962</t>
+          <t>83097</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>117160</t>
+          <t>116011</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6361,12 +6361,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>21,46%</t>
+          <t>22,03%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>31,06%</t>
+          <t>30,75%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6381,12 +6381,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>98661</t>
+          <t>101520</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>137052</t>
+          <t>138468</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6396,12 +6396,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>26,5%</t>
+          <t>27,27%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>36,81%</t>
+          <t>37,2%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6416,12 +6416,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>189679</t>
+          <t>193170</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>242738</t>
+          <t>242142</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -6431,12 +6431,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>25,31%</t>
+          <t>25,77%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>32,39%</t>
+          <t>32,31%</t>
         </is>
       </c>
     </row>
@@ -6459,12 +6459,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>260067</t>
+          <t>261216</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>296265</t>
+          <t>294130</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6474,12 +6474,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>68,94%</t>
+          <t>69,25%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>78,54%</t>
+          <t>77,97%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6494,12 +6494,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>235221</t>
+          <t>233805</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>273612</t>
+          <t>270753</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6509,12 +6509,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>63,19%</t>
+          <t>62,8%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>73,5%</t>
+          <t>72,73%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6529,12 +6529,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>506762</t>
+          <t>507358</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>559821</t>
+          <t>556330</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6544,12 +6544,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>67,61%</t>
+          <t>67,69%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>74,69%</t>
+          <t>74,23%</t>
         </is>
       </c>
     </row>
@@ -6689,12 +6689,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>170413</t>
+          <t>170590</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>215925</t>
+          <t>216776</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6704,12 +6704,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>32,65%</t>
+          <t>32,69%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>41,37%</t>
+          <t>41,53%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6724,12 +6724,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>56755</t>
+          <t>55737</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>83072</t>
+          <t>82464</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6739,12 +6739,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>34,16%</t>
+          <t>33,55%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>50,01%</t>
+          <t>49,64%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6759,12 +6759,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>237020</t>
+          <t>236525</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>288422</t>
+          <t>291722</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6774,12 +6774,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>34,45%</t>
+          <t>34,38%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>41,92%</t>
+          <t>42,4%</t>
         </is>
       </c>
     </row>
@@ -6802,12 +6802,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>305989</t>
+          <t>305138</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>351501</t>
+          <t>351324</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6817,12 +6817,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>58,63%</t>
+          <t>58,47%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>67,35%</t>
+          <t>67,31%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6837,12 +6837,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>83051</t>
+          <t>83659</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>109368</t>
+          <t>110386</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6852,12 +6852,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>49,99%</t>
+          <t>50,36%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>65,84%</t>
+          <t>66,45%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6872,12 +6872,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>399614</t>
+          <t>396314</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>451016</t>
+          <t>451511</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6887,12 +6887,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>58,08%</t>
+          <t>57,6%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>65,55%</t>
+          <t>65,62%</t>
         </is>
       </c>
     </row>
@@ -7032,12 +7032,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>410669</t>
+          <t>412712</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>476560</t>
+          <t>478617</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7047,12 +7047,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>35,72%</t>
+          <t>35,9%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>41,45%</t>
+          <t>41,63%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>325611</t>
+          <t>323709</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>382078</t>
+          <t>380855</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7082,12 +7082,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>39,43%</t>
+          <t>39,2%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>46,26%</t>
+          <t>46,12%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7102,12 +7102,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>751111</t>
+          <t>749896</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>839328</t>
+          <t>840487</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7117,12 +7117,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>38,02%</t>
+          <t>37,96%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>42,49%</t>
+          <t>42,55%</t>
         </is>
       </c>
     </row>
@@ -7145,12 +7145,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>673078</t>
+          <t>671021</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>738969</t>
+          <t>736926</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7160,12 +7160,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>58,55%</t>
+          <t>58,37%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>64,28%</t>
+          <t>64,1%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7180,12 +7180,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>443798</t>
+          <t>445021</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>500265</t>
+          <t>502167</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7195,12 +7195,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>53,74%</t>
+          <t>53,88%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>60,57%</t>
+          <t>60,8%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7215,12 +7215,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1136186</t>
+          <t>1135027</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1224403</t>
+          <t>1225618</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7230,12 +7230,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>57,51%</t>
+          <t>57,45%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>61,98%</t>
+          <t>62,04%</t>
         </is>
       </c>
     </row>
@@ -7375,12 +7375,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>227743</t>
+          <t>229678</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>280765</t>
+          <t>279124</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7390,12 +7390,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>36,69%</t>
+          <t>37,0%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>45,23%</t>
+          <t>44,97%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7410,12 +7410,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>324836</t>
+          <t>326332</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>382271</t>
+          <t>380816</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7425,12 +7425,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>44,0%</t>
+          <t>44,2%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>51,78%</t>
+          <t>51,58%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7445,12 +7445,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>568876</t>
+          <t>569396</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>645757</t>
+          <t>644261</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7460,12 +7460,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>41,86%</t>
+          <t>41,9%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>47,52%</t>
+          <t>47,41%</t>
         </is>
       </c>
     </row>
@@ -7488,12 +7488,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>339941</t>
+          <t>341582</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>392963</t>
+          <t>391028</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7503,12 +7503,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>54,77%</t>
+          <t>55,03%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>63,31%</t>
+          <t>63,0%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7523,12 +7523,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>355973</t>
+          <t>357428</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>413408</t>
+          <t>411912</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7538,12 +7538,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>48,22%</t>
+          <t>48,42%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>56,0%</t>
+          <t>55,8%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7558,12 +7558,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>713193</t>
+          <t>714689</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>790074</t>
+          <t>789554</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7573,12 +7573,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>52,48%</t>
+          <t>52,59%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>58,14%</t>
+          <t>58,1%</t>
         </is>
       </c>
     </row>
@@ -7718,12 +7718,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>37748</t>
+          <t>37689</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>64398</t>
+          <t>65078</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -7733,12 +7733,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>13,15%</t>
+          <t>13,13%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>22,43%</t>
+          <t>22,66%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -7753,12 +7753,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>483036</t>
+          <t>482644</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>547320</t>
+          <t>551156</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -7768,12 +7768,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>44,64%</t>
+          <t>44,61%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>50,58%</t>
+          <t>50,94%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -7788,12 +7788,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>528807</t>
+          <t>525764</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>601896</t>
+          <t>605471</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -7803,12 +7803,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>38,62%</t>
+          <t>38,4%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>43,96%</t>
+          <t>44,22%</t>
         </is>
       </c>
     </row>
@@ -7831,12 +7831,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>222747</t>
+          <t>222067</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>249397</t>
+          <t>249456</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -7846,12 +7846,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>77,57%</t>
+          <t>77,34%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>86,85%</t>
+          <t>86,87%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -7866,12 +7866,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>534705</t>
+          <t>530869</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>598989</t>
+          <t>599381</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7881,12 +7881,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>49,42%</t>
+          <t>49,06%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>55,36%</t>
+          <t>55,39%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7901,12 +7901,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>767274</t>
+          <t>763699</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>840363</t>
+          <t>843406</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7916,12 +7916,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>56,04%</t>
+          <t>55,78%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>61,38%</t>
+          <t>61,6%</t>
         </is>
       </c>
     </row>
@@ -8061,12 +8061,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>1085640</t>
+          <t>1086798</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>1194549</t>
+          <t>1202082</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8076,12 +8076,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>32,07%</t>
+          <t>32,1%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>35,28%</t>
+          <t>35,5%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8096,12 +8096,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>1443695</t>
+          <t>1442034</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>1569061</t>
+          <t>1565095</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8111,12 +8111,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>40,88%</t>
+          <t>40,83%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>44,43%</t>
+          <t>44,32%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8131,12 +8131,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>2577641</t>
+          <t>2564872</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>2742784</t>
+          <t>2737444</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8146,12 +8146,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>37,26%</t>
+          <t>37,08%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>39,65%</t>
+          <t>39,57%</t>
         </is>
       </c>
     </row>
@@ -8174,12 +8174,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>2191173</t>
+          <t>2183640</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>2300082</t>
+          <t>2298924</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8189,12 +8189,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>64,72%</t>
+          <t>64,5%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>67,93%</t>
+          <t>67,9%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8209,12 +8209,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>1962535</t>
+          <t>1966501</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>2087901</t>
+          <t>2089562</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8224,12 +8224,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>55,57%</t>
+          <t>55,68%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>59,12%</t>
+          <t>59,17%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8244,12 +8244,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>4174534</t>
+          <t>4179874</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>4339677</t>
+          <t>4352446</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8259,12 +8259,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>60,35%</t>
+          <t>60,43%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>62,74%</t>
+          <t>62,92%</t>
         </is>
       </c>
     </row>
@@ -8443,7 +8443,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que no realiza actividad física en su tiempo libre en 2023</t>
+          <t>Población que no realiza actividad física en su tiempo libre en 2023 (tasa de respuesta: 99,76%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -8638,12 +8638,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>115533</t>
+          <t>115610</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>156087</t>
+          <t>156899</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -8653,82 +8653,82 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
+          <t>23,0%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>31,21%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>161</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>103807</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>88230</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>118907</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>23,2%</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="inlineStr">
+        <is>
+          <t>19,72%</t>
+        </is>
+      </c>
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>26,57%</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
+        <is>
+          <t>306</t>
+        </is>
+      </c>
+      <c r="R4" s="2" t="inlineStr">
+        <is>
+          <t>239981</t>
+        </is>
+      </c>
+      <c r="S4" s="2" t="inlineStr">
+        <is>
+          <t>218351</t>
+        </is>
+      </c>
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>268020</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
+        <is>
+          <t>25,26%</t>
+        </is>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
+        <is>
           <t>22,98%</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>31,05%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>161</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>103807</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>89372</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>119433</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>23,2%</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>19,97%</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>26,69%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>306</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>239981</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>214854</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>263545</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>25,26%</t>
-        </is>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>22,61%</t>
-        </is>
-      </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>27,74%</t>
+          <t>28,21%</t>
         </is>
       </c>
     </row>
@@ -8751,12 +8751,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>346580</t>
+          <t>345768</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>387134</t>
+          <t>387057</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -8766,82 +8766,82 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>68,95%</t>
+          <t>68,79%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
+          <t>77,0%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>525</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>343660</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>328560</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>359237</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>76,8%</t>
+        </is>
+      </c>
+      <c r="O5" s="2" t="inlineStr">
+        <is>
+          <t>73,43%</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="inlineStr">
+        <is>
+          <t>80,28%</t>
+        </is>
+      </c>
+      <c r="Q5" s="2" t="inlineStr">
+        <is>
+          <t>932</t>
+        </is>
+      </c>
+      <c r="R5" s="2" t="inlineStr">
+        <is>
+          <t>710153</t>
+        </is>
+      </c>
+      <c r="S5" s="2" t="inlineStr">
+        <is>
+          <t>682114</t>
+        </is>
+      </c>
+      <c r="T5" s="2" t="inlineStr">
+        <is>
+          <t>731783</t>
+        </is>
+      </c>
+      <c r="U5" s="2" t="inlineStr">
+        <is>
+          <t>74,74%</t>
+        </is>
+      </c>
+      <c r="V5" s="2" t="inlineStr">
+        <is>
+          <t>71,79%</t>
+        </is>
+      </c>
+      <c r="W5" s="2" t="inlineStr">
+        <is>
           <t>77,02%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>525</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>343660</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>328034</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>358095</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>76,8%</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>73,31%</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>80,03%</t>
-        </is>
-      </c>
-      <c r="Q5" s="2" t="inlineStr">
-        <is>
-          <t>932</t>
-        </is>
-      </c>
-      <c r="R5" s="2" t="inlineStr">
-        <is>
-          <t>710153</t>
-        </is>
-      </c>
-      <c r="S5" s="2" t="inlineStr">
-        <is>
-          <t>686589</t>
-        </is>
-      </c>
-      <c r="T5" s="2" t="inlineStr">
-        <is>
-          <t>735280</t>
-        </is>
-      </c>
-      <c r="U5" s="2" t="inlineStr">
-        <is>
-          <t>74,74%</t>
-        </is>
-      </c>
-      <c r="V5" s="2" t="inlineStr">
-        <is>
-          <t>72,26%</t>
-        </is>
-      </c>
-      <c r="W5" s="2" t="inlineStr">
-        <is>
-          <t>77,39%</t>
         </is>
       </c>
     </row>
@@ -8981,12 +8981,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>98296</t>
+          <t>96089</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>135700</t>
+          <t>135938</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -8996,12 +8996,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>21,74%</t>
+          <t>21,25%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>30,01%</t>
+          <t>30,06%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -9016,12 +9016,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>111458</t>
+          <t>110953</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>141164</t>
+          <t>141499</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -9031,12 +9031,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>29,13%</t>
+          <t>29,0%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>36,9%</t>
+          <t>36,99%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -9051,12 +9051,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>216343</t>
+          <t>218861</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>264089</t>
+          <t>265981</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -9066,12 +9066,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>25,92%</t>
+          <t>26,22%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>31,64%</t>
+          <t>31,86%</t>
         </is>
       </c>
     </row>
@@ -9094,12 +9094,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>316513</t>
+          <t>316275</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>353917</t>
+          <t>356124</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -9109,12 +9109,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>69,99%</t>
+          <t>69,94%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>78,26%</t>
+          <t>78,75%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -9129,12 +9129,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>241416</t>
+          <t>241081</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>271122</t>
+          <t>271627</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -9144,12 +9144,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>63,1%</t>
+          <t>63,01%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>70,87%</t>
+          <t>71,0%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -9164,12 +9164,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>570704</t>
+          <t>568812</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>618450</t>
+          <t>615932</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -9179,12 +9179,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>68,36%</t>
+          <t>68,14%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>74,08%</t>
+          <t>73,78%</t>
         </is>
       </c>
     </row>
@@ -9324,12 +9324,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>60592</t>
+          <t>61548</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>261856</t>
+          <t>261384</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -9339,12 +9339,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>9,08%</t>
+          <t>9,22%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>39,24%</t>
+          <t>39,17%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -9359,12 +9359,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>57768</t>
+          <t>57382</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>78117</t>
+          <t>77412</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -9374,12 +9374,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>34,64%</t>
+          <t>34,41%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>46,85%</t>
+          <t>46,42%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -9394,12 +9394,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>98423</t>
+          <t>83731</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>329791</t>
+          <t>329571</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -9409,12 +9409,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>11,8%</t>
+          <t>10,04%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>39,54%</t>
+          <t>39,52%</t>
         </is>
       </c>
     </row>
@@ -9437,12 +9437,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>405418</t>
+          <t>405890</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>606682</t>
+          <t>605726</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -9452,12 +9452,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>60,76%</t>
+          <t>60,83%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>90,92%</t>
+          <t>90,78%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -9472,12 +9472,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>88632</t>
+          <t>89337</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>108981</t>
+          <t>109367</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -9487,12 +9487,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>53,15%</t>
+          <t>53,58%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>65,36%</t>
+          <t>65,59%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -9507,12 +9507,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>504231</t>
+          <t>504451</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>735599</t>
+          <t>750291</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -9522,12 +9522,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>60,46%</t>
+          <t>60,48%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>88,2%</t>
+          <t>89,96%</t>
         </is>
       </c>
     </row>
@@ -9667,12 +9667,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>364522</t>
+          <t>363758</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>428663</t>
+          <t>429817</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -9682,12 +9682,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>35,35%</t>
+          <t>35,28%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>41,57%</t>
+          <t>41,68%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -9702,12 +9702,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>166264</t>
+          <t>156345</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>395701</t>
+          <t>396440</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -9717,12 +9717,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>17,01%</t>
+          <t>15,99%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>40,48%</t>
+          <t>40,55%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -9737,12 +9737,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>475889</t>
+          <t>452640</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>797087</t>
+          <t>794756</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -9752,12 +9752,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>23,69%</t>
+          <t>22,53%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>39,68%</t>
+          <t>39,57%</t>
         </is>
       </c>
     </row>
@@ -9780,12 +9780,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>602473</t>
+          <t>601319</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>666614</t>
+          <t>667378</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -9795,12 +9795,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>58,43%</t>
+          <t>58,32%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>64,65%</t>
+          <t>64,72%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9815,12 +9815,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>581855</t>
+          <t>581116</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>811292</t>
+          <t>821211</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -9830,12 +9830,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>59,52%</t>
+          <t>59,45%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>82,99%</t>
+          <t>84,01%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9850,12 +9850,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1211605</t>
+          <t>1213936</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1532803</t>
+          <t>1556052</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -9865,12 +9865,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>60,32%</t>
+          <t>60,43%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>76,31%</t>
+          <t>77,47%</t>
         </is>
       </c>
     </row>
@@ -10010,12 +10010,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>181109</t>
+          <t>181019</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>226536</t>
+          <t>227505</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -10025,12 +10025,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>38,29%</t>
+          <t>38,27%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>47,89%</t>
+          <t>48,1%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -10045,12 +10045,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>285123</t>
+          <t>286157</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>433300</t>
+          <t>432992</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -10060,12 +10060,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>34,06%</t>
+          <t>34,19%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>51,76%</t>
+          <t>51,73%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -10080,12 +10080,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>491240</t>
+          <t>486407</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>642255</t>
+          <t>638352</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -10095,12 +10095,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>37,5%</t>
+          <t>37,13%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>49,02%</t>
+          <t>48,73%</t>
         </is>
       </c>
     </row>
@@ -10123,12 +10123,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>246457</t>
+          <t>245488</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>291884</t>
+          <t>291974</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -10138,12 +10138,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>52,11%</t>
+          <t>51,9%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>61,71%</t>
+          <t>61,73%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -10158,12 +10158,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>403769</t>
+          <t>404077</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>551946</t>
+          <t>550912</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -10173,12 +10173,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>48,24%</t>
+          <t>48,27%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>65,94%</t>
+          <t>65,81%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -10193,12 +10193,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>667806</t>
+          <t>671709</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>818821</t>
+          <t>823654</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -10208,12 +10208,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>50,98%</t>
+          <t>51,27%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>62,5%</t>
+          <t>62,87%</t>
         </is>
       </c>
     </row>
@@ -10353,12 +10353,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>17022</t>
+          <t>16830</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>59302</t>
+          <t>58535</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -10368,12 +10368,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>7,08%</t>
+          <t>7,0%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>24,66%</t>
+          <t>24,34%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -10388,12 +10388,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>348638</t>
+          <t>348819</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>398938</t>
+          <t>399139</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -10403,12 +10403,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>45,96%</t>
+          <t>45,99%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>52,59%</t>
+          <t>52,62%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -10423,12 +10423,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>371475</t>
+          <t>371097</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>438990</t>
+          <t>439279</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -10438,12 +10438,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>37,18%</t>
+          <t>37,15%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>43,94%</t>
+          <t>43,97%</t>
         </is>
       </c>
     </row>
@@ -10466,12 +10466,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>181205</t>
+          <t>181972</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>223485</t>
+          <t>223677</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -10481,12 +10481,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>75,34%</t>
+          <t>75,66%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>92,92%</t>
+          <t>93,0%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -10501,12 +10501,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>359597</t>
+          <t>359396</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>409897</t>
+          <t>409716</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -10516,12 +10516,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>47,41%</t>
+          <t>47,38%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>54,04%</t>
+          <t>54,01%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -10536,12 +10536,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>560052</t>
+          <t>559763</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>627567</t>
+          <t>627945</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -10551,12 +10551,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>56,06%</t>
+          <t>56,03%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>62,82%</t>
+          <t>62,85%</t>
         </is>
       </c>
     </row>
@@ -10696,12 +10696,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>800039</t>
+          <t>809885</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>1141227</t>
+          <t>1147027</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -10711,12 +10711,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>23,76%</t>
+          <t>24,06%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>33,9%</t>
+          <t>34,07%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10731,12 +10731,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>1103162</t>
+          <t>1117116</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>1476421</t>
+          <t>1481180</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -10746,12 +10746,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>30,9%</t>
+          <t>31,29%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>41,36%</t>
+          <t>41,49%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10766,12 +10766,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>2065499</t>
+          <t>2131689</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>2570836</t>
+          <t>2577856</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -10781,12 +10781,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>29,78%</t>
+          <t>30,73%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>37,06%</t>
+          <t>37,16%</t>
         </is>
       </c>
     </row>
@@ -10809,12 +10809,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>2225562</t>
+          <t>2219762</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>2566750</t>
+          <t>2556904</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -10824,12 +10824,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>66,1%</t>
+          <t>65,93%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>76,24%</t>
+          <t>75,94%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -10844,12 +10844,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>2093535</t>
+          <t>2088776</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>2466794</t>
+          <t>2452840</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -10859,12 +10859,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>58,64%</t>
+          <t>58,51%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>69,1%</t>
+          <t>68,71%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -10879,12 +10879,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>4365909</t>
+          <t>4358889</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>4871246</t>
+          <t>4805056</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -10894,12 +10894,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>62,94%</t>
+          <t>62,84%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>70,22%</t>
+          <t>69,27%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P34A_R-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P34A_R-Clase-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>142312</t>
+          <t>144075</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>184169</t>
+          <t>184622</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>30,31%</t>
+          <t>30,68%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>39,22%</t>
+          <t>39,32%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>94224</t>
+          <t>92564</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>127767</t>
+          <t>126607</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>31,42%</t>
+          <t>30,87%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>42,61%</t>
+          <t>42,22%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>250987</t>
+          <t>248428</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>305476</t>
+          <t>301257</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>32,62%</t>
+          <t>32,29%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>39,7%</t>
+          <t>39,15%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>285402</t>
+          <t>284949</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>327259</t>
+          <t>325496</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>60,78%</t>
+          <t>60,68%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>69,69%</t>
+          <t>69,32%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>172112</t>
+          <t>173272</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>205655</t>
+          <t>207315</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>57,39%</t>
+          <t>57,78%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>68,58%</t>
+          <t>69,13%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>463974</t>
+          <t>468193</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>518463</t>
+          <t>521022</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>60,3%</t>
+          <t>60,85%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>67,38%</t>
+          <t>67,71%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>90968</t>
+          <t>91324</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>126967</t>
+          <t>126455</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>25,2%</t>
+          <t>25,3%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>35,17%</t>
+          <t>35,03%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>136031</t>
+          <t>136399</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>174443</t>
+          <t>173762</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>37,42%</t>
+          <t>37,53%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>47,99%</t>
+          <t>47,8%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>236754</t>
+          <t>236641</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>290651</t>
+          <t>289772</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>32,68%</t>
+          <t>32,66%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>40,12%</t>
+          <t>40,0%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>234003</t>
+          <t>234515</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>270002</t>
+          <t>269646</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>64,83%</t>
+          <t>64,97%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>74,8%</t>
+          <t>74,7%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>189041</t>
+          <t>189722</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>227453</t>
+          <t>227085</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>52,01%</t>
+          <t>52,2%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>62,58%</t>
+          <t>62,47%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>433803</t>
+          <t>434682</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>487700</t>
+          <t>487813</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>59,88%</t>
+          <t>60,0%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>67,32%</t>
+          <t>67,34%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>225365</t>
+          <t>225269</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>272134</t>
+          <t>272651</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>41,91%</t>
+          <t>41,89%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>50,61%</t>
+          <t>50,71%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>64567</t>
+          <t>64699</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>89938</t>
+          <t>88742</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>39,21%</t>
+          <t>39,29%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>54,62%</t>
+          <t>53,89%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>299517</t>
+          <t>300171</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>351953</t>
+          <t>354362</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>42,64%</t>
+          <t>42,74%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>50,11%</t>
+          <t>50,45%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>265582</t>
+          <t>265065</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>312351</t>
+          <t>312447</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>49,39%</t>
+          <t>49,29%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>58,09%</t>
+          <t>58,11%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>74723</t>
+          <t>75919</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>100094</t>
+          <t>99962</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>45,38%</t>
+          <t>46,11%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>60,79%</t>
+          <t>60,71%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>350424</t>
+          <t>348015</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>402860</t>
+          <t>402206</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>49,89%</t>
+          <t>49,55%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>57,36%</t>
+          <t>57,26%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>537300</t>
+          <t>537051</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>606314</t>
+          <t>606581</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>44,16%</t>
+          <t>44,14%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>49,83%</t>
+          <t>49,85%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>307051</t>
+          <t>309817</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>360463</t>
+          <t>361691</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>43,44%</t>
+          <t>43,83%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>51,0%</t>
+          <t>51,17%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>863633</t>
+          <t>863172</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>954337</t>
+          <t>951588</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>44,9%</t>
+          <t>44,87%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>49,61%</t>
+          <t>49,47%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>610484</t>
+          <t>610217</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>679498</t>
+          <t>679747</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>50,17%</t>
+          <t>50,15%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>55,84%</t>
+          <t>55,86%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>346325</t>
+          <t>345097</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>399737</t>
+          <t>396971</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>49,0%</t>
+          <t>48,83%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>56,56%</t>
+          <t>56,17%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>969249</t>
+          <t>971998</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1059953</t>
+          <t>1060414</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>50,39%</t>
+          <t>50,53%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>55,1%</t>
+          <t>55,13%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>155952</t>
+          <t>154257</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>194065</t>
+          <t>191375</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>45,49%</t>
+          <t>44,99%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>56,6%</t>
+          <t>55,82%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>276463</t>
+          <t>274369</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>325627</t>
+          <t>325366</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>49,8%</t>
+          <t>49,43%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>58,66%</t>
+          <t>58,61%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>441394</t>
+          <t>442228</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>503726</t>
+          <t>506402</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>49,16%</t>
+          <t>49,25%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>56,1%</t>
+          <t>56,39%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>148788</t>
+          <t>151478</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>186901</t>
+          <t>188596</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>43,4%</t>
+          <t>44,18%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>54,51%</t>
+          <t>55,01%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>229481</t>
+          <t>229742</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>278645</t>
+          <t>280739</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>41,34%</t>
+          <t>41,39%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>50,2%</t>
+          <t>50,57%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>394235</t>
+          <t>391559</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>456567</t>
+          <t>455733</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>43,9%</t>
+          <t>43,61%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>50,84%</t>
+          <t>50,75%</t>
         </is>
       </c>
     </row>
@@ -2428,7 +2428,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>43502</t>
+          <t>43978</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>71598</t>
+          <t>70829</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>14,63%</t>
+          <t>14,79%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>24,08%</t>
+          <t>23,82%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>516174</t>
+          <t>517959</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>585323</t>
+          <t>586831</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>42,04%</t>
+          <t>42,19%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>47,67%</t>
+          <t>47,8%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>570101</t>
+          <t>571996</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>644370</t>
+          <t>646503</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>37,38%</t>
+          <t>37,51%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>42,25%</t>
+          <t>42,39%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>225704</t>
+          <t>226473</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>253800</t>
+          <t>253324</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,12 +2576,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>75,92%</t>
+          <t>76,18%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>85,37%</t>
+          <t>85,21%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>642442</t>
+          <t>640934</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>711591</t>
+          <t>709806</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>52,33%</t>
+          <t>52,2%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>57,96%</t>
+          <t>57,81%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>880697</t>
+          <t>878564</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>954966</t>
+          <t>953071</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>57,75%</t>
+          <t>57,61%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>62,62%</t>
+          <t>62,49%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>1264464</t>
+          <t>1264571</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>1381625</t>
+          <t>1381502</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2811,7 +2811,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>42,84%</t>
+          <t>42,83%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>1475555</t>
+          <t>1472806</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>1589148</t>
+          <t>1585929</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>44,48%</t>
+          <t>44,39%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>47,9%</t>
+          <t>47,8%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>2769556</t>
+          <t>2768484</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>2929625</t>
+          <t>2932319</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>42,33%</t>
+          <t>42,31%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>44,78%</t>
+          <t>44,82%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>1843585</t>
+          <t>1843708</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>1960746</t>
+          <t>1960639</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,7 +2919,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>57,16%</t>
+          <t>57,17%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>1728538</t>
+          <t>1731757</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>1842131</t>
+          <t>1844880</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>52,1%</t>
+          <t>52,2%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>55,52%</t>
+          <t>55,61%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>3613271</t>
+          <t>3610577</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>3773340</t>
+          <t>3774412</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>55,22%</t>
+          <t>55,18%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>57,67%</t>
+          <t>57,69%</t>
         </is>
       </c>
     </row>
@@ -3368,12 +3368,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>53725</t>
+          <t>53628</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>86688</t>
+          <t>85350</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3383,12 +3383,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>12,29%</t>
+          <t>12,27%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>19,83%</t>
+          <t>19,52%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3403,12 +3403,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>52108</t>
+          <t>53577</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>82216</t>
+          <t>83638</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3418,12 +3418,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>16,57%</t>
+          <t>17,04%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>26,15%</t>
+          <t>26,6%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3438,12 +3438,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>113504</t>
+          <t>114795</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>159970</t>
+          <t>160193</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3453,12 +3453,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>15,1%</t>
+          <t>15,27%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>21,28%</t>
+          <t>21,31%</t>
         </is>
       </c>
     </row>
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>350523</t>
+          <t>351861</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>383486</t>
+          <t>383583</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3496,12 +3496,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>80,17%</t>
+          <t>80,48%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>87,71%</t>
+          <t>87,73%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3516,12 +3516,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>232238</t>
+          <t>230816</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>262346</t>
+          <t>260877</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3531,12 +3531,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>73,85%</t>
+          <t>73,4%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>83,43%</t>
+          <t>82,96%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3551,12 +3551,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>591695</t>
+          <t>591472</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>638161</t>
+          <t>636870</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3566,12 +3566,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>78,72%</t>
+          <t>78,69%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>84,9%</t>
+          <t>84,73%</t>
         </is>
       </c>
     </row>
@@ -3711,12 +3711,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>60368</t>
+          <t>60001</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>94623</t>
+          <t>92057</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3726,12 +3726,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>14,41%</t>
+          <t>14,33%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>22,59%</t>
+          <t>21,98%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3746,12 +3746,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>71716</t>
+          <t>71324</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>105899</t>
+          <t>104894</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3761,12 +3761,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>21,22%</t>
+          <t>21,1%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>31,33%</t>
+          <t>31,03%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3781,12 +3781,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>136325</t>
+          <t>138569</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>185898</t>
+          <t>187170</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3796,12 +3796,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>18,01%</t>
+          <t>18,31%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>24,56%</t>
+          <t>24,73%</t>
         </is>
       </c>
     </row>
@@ -3824,12 +3824,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>324174</t>
+          <t>326740</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>358429</t>
+          <t>358796</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3839,12 +3839,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>77,41%</t>
+          <t>78,02%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>85,59%</t>
+          <t>85,67%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3859,12 +3859,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>232112</t>
+          <t>233117</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>266295</t>
+          <t>266687</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3874,12 +3874,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>68,67%</t>
+          <t>68,97%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>78,78%</t>
+          <t>78,9%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3894,12 +3894,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>570910</t>
+          <t>569638</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>620483</t>
+          <t>618239</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3909,12 +3909,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>75,44%</t>
+          <t>75,27%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>81,99%</t>
+          <t>81,69%</t>
         </is>
       </c>
     </row>
@@ -4054,12 +4054,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>138964</t>
+          <t>137377</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>183250</t>
+          <t>183153</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4069,12 +4069,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>22,11%</t>
+          <t>21,86%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>29,16%</t>
+          <t>29,14%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4089,12 +4089,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>77219</t>
+          <t>76394</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>107661</t>
+          <t>107214</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4104,12 +4104,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>29,68%</t>
+          <t>29,37%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>41,39%</t>
+          <t>41,22%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4124,12 +4124,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>221465</t>
+          <t>225348</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>279296</t>
+          <t>279469</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4139,12 +4139,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>24,92%</t>
+          <t>25,36%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>31,43%</t>
+          <t>31,45%</t>
         </is>
       </c>
     </row>
@@ -4167,12 +4167,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>445268</t>
+          <t>445365</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>489554</t>
+          <t>491141</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4182,12 +4182,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>70,84%</t>
+          <t>70,86%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>77,89%</t>
+          <t>78,14%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4202,12 +4202,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>152468</t>
+          <t>152915</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>182910</t>
+          <t>183735</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4217,12 +4217,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>58,61%</t>
+          <t>58,78%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>70,32%</t>
+          <t>70,63%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4237,12 +4237,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>609351</t>
+          <t>609178</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>667182</t>
+          <t>663299</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4252,12 +4252,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>68,57%</t>
+          <t>68,55%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>75,08%</t>
+          <t>74,64%</t>
         </is>
       </c>
     </row>
@@ -4397,12 +4397,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>264394</t>
+          <t>263702</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>324860</t>
+          <t>323329</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4412,12 +4412,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>22,83%</t>
+          <t>22,77%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>28,05%</t>
+          <t>27,92%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4432,12 +4432,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>210990</t>
+          <t>208760</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>262904</t>
+          <t>262012</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4447,12 +4447,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>27,52%</t>
+          <t>27,23%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>34,29%</t>
+          <t>34,18%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4467,12 +4467,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>491982</t>
+          <t>492143</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>574200</t>
+          <t>573385</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4482,12 +4482,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>25,56%</t>
+          <t>25,57%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>29,83%</t>
+          <t>29,79%</t>
         </is>
       </c>
     </row>
@@ -4510,12 +4510,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>833288</t>
+          <t>834819</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>893754</t>
+          <t>894446</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4525,12 +4525,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>71,95%</t>
+          <t>72,08%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>77,17%</t>
+          <t>77,23%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4545,12 +4545,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>503753</t>
+          <t>504645</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>555667</t>
+          <t>557897</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>65,71%</t>
+          <t>65,82%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>72,48%</t>
+          <t>72,77%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4580,12 +4580,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1350606</t>
+          <t>1351421</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1432824</t>
+          <t>1432663</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4595,12 +4595,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>70,17%</t>
+          <t>70,21%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>74,44%</t>
+          <t>74,43%</t>
         </is>
       </c>
     </row>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>125278</t>
+          <t>125231</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>165570</t>
+          <t>165702</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4755,12 +4755,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>24,54%</t>
+          <t>24,53%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>32,43%</t>
+          <t>32,45%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>254444</t>
+          <t>251897</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>307500</t>
+          <t>307539</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4790,7 +4790,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>33,41%</t>
+          <t>33,08%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>389220</t>
+          <t>392420</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>457323</t>
+          <t>460617</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>30,6%</t>
+          <t>30,85%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>35,95%</t>
+          <t>36,21%</t>
         </is>
       </c>
     </row>
@@ -4853,12 +4853,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>345026</t>
+          <t>344894</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>385318</t>
+          <t>385365</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4868,12 +4868,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>67,57%</t>
+          <t>67,55%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>75,46%</t>
+          <t>75,47%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4888,12 +4888,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>454022</t>
+          <t>453983</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>507078</t>
+          <t>509625</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4908,7 +4908,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>66,59%</t>
+          <t>66,92%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4923,12 +4923,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>814795</t>
+          <t>811501</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>882898</t>
+          <t>879698</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4938,12 +4938,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>64,05%</t>
+          <t>63,79%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>69,4%</t>
+          <t>69,15%</t>
         </is>
       </c>
     </row>
@@ -5063,7 +5063,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -5083,12 +5083,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>21132</t>
+          <t>21766</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>41629</t>
+          <t>43194</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>7,92%</t>
+          <t>8,16%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>15,6%</t>
+          <t>16,18%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>305915</t>
+          <t>307166</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>365981</t>
+          <t>366688</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>27,6%</t>
+          <t>27,72%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>33,02%</t>
+          <t>33,09%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>336640</t>
+          <t>335362</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>403330</t>
+          <t>402017</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>24,48%</t>
+          <t>24,39%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>29,33%</t>
+          <t>29,23%</t>
         </is>
       </c>
     </row>
@@ -5196,12 +5196,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>225253</t>
+          <t>223688</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>245750</t>
+          <t>245116</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5211,12 +5211,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>84,4%</t>
+          <t>83,82%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>92,08%</t>
+          <t>91,84%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5231,12 +5231,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>742273</t>
+          <t>741566</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>802339</t>
+          <t>801088</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5246,12 +5246,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>66,98%</t>
+          <t>66,91%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>72,4%</t>
+          <t>72,28%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5266,12 +5266,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>971806</t>
+          <t>973119</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1038496</t>
+          <t>1039774</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5281,12 +5281,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>70,67%</t>
+          <t>70,77%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>75,52%</t>
+          <t>75,61%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>720172</t>
+          <t>721199</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>817726</t>
+          <t>820342</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>21,06%</t>
+          <t>21,09%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>23,91%</t>
+          <t>23,99%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>1043274</t>
+          <t>1042372</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>1154818</t>
+          <t>1157073</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>29,4%</t>
+          <t>29,37%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>32,54%</t>
+          <t>32,6%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1790240</t>
+          <t>1787521</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1936669</t>
+          <t>1939629</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>25,69%</t>
+          <t>25,65%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>27,79%</t>
+          <t>27,83%</t>
         </is>
       </c>
     </row>
@@ -5539,12 +5539,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>2602426</t>
+          <t>2599810</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>2699980</t>
+          <t>2698953</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5554,12 +5554,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>76,09%</t>
+          <t>76,01%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>78,94%</t>
+          <t>78,91%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5574,12 +5574,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>2394210</t>
+          <t>2391955</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>2505754</t>
+          <t>2506656</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5589,12 +5589,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>67,46%</t>
+          <t>67,4%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>70,6%</t>
+          <t>70,63%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5609,12 +5609,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>5032511</t>
+          <t>5029551</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>5178940</t>
+          <t>5181659</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5624,12 +5624,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>72,21%</t>
+          <t>72,17%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>74,31%</t>
+          <t>74,35%</t>
         </is>
       </c>
     </row>
@@ -6003,12 +6003,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>90840</t>
+          <t>91022</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>127857</t>
+          <t>127799</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6018,12 +6018,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>21,17%</t>
+          <t>21,21%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>29,8%</t>
+          <t>29,78%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6038,12 +6038,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>81061</t>
+          <t>82401</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>114874</t>
+          <t>116184</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6053,12 +6053,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>23,36%</t>
+          <t>23,74%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>33,1%</t>
+          <t>33,48%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6073,12 +6073,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>183991</t>
+          <t>181509</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>231684</t>
+          <t>233156</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6088,12 +6088,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>23,71%</t>
+          <t>23,39%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>29,85%</t>
+          <t>30,04%</t>
         </is>
       </c>
     </row>
@@ -6116,12 +6116,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>301235</t>
+          <t>301293</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>338252</t>
+          <t>338070</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6131,12 +6131,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>70,2%</t>
+          <t>70,22%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>78,83%</t>
+          <t>78,79%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6151,12 +6151,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>232181</t>
+          <t>230871</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>265994</t>
+          <t>264654</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6166,12 +6166,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>66,9%</t>
+          <t>66,52%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>76,64%</t>
+          <t>76,26%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6186,12 +6186,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>544463</t>
+          <t>542991</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>592156</t>
+          <t>594638</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6201,12 +6201,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>70,15%</t>
+          <t>69,96%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>76,29%</t>
+          <t>76,61%</t>
         </is>
       </c>
     </row>
@@ -6346,12 +6346,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>83097</t>
+          <t>81967</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>116011</t>
+          <t>116523</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6361,12 +6361,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>22,03%</t>
+          <t>21,73%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>30,75%</t>
+          <t>30,89%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6381,12 +6381,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>101520</t>
+          <t>100022</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>138468</t>
+          <t>137612</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6396,12 +6396,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>27,27%</t>
+          <t>26,87%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>37,2%</t>
+          <t>36,97%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6416,12 +6416,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>193170</t>
+          <t>193042</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>242142</t>
+          <t>241860</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -6431,12 +6431,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>25,77%</t>
+          <t>25,76%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>32,31%</t>
+          <t>32,27%</t>
         </is>
       </c>
     </row>
@@ -6459,12 +6459,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>261216</t>
+          <t>260704</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>294130</t>
+          <t>295260</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6474,12 +6474,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>69,25%</t>
+          <t>69,11%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>77,97%</t>
+          <t>78,27%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6494,12 +6494,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>233805</t>
+          <t>234661</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>270753</t>
+          <t>272251</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6509,12 +6509,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>62,8%</t>
+          <t>63,03%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>72,73%</t>
+          <t>73,13%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6529,12 +6529,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>507358</t>
+          <t>507640</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>556330</t>
+          <t>556458</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6544,12 +6544,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>67,69%</t>
+          <t>67,73%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>74,23%</t>
+          <t>74,24%</t>
         </is>
       </c>
     </row>
@@ -6689,12 +6689,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>170590</t>
+          <t>170918</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>216776</t>
+          <t>216837</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6704,12 +6704,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>32,69%</t>
+          <t>32,75%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>41,53%</t>
+          <t>41,55%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6724,12 +6724,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>55737</t>
+          <t>57216</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>82464</t>
+          <t>84422</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6739,12 +6739,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>33,55%</t>
+          <t>34,44%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>49,64%</t>
+          <t>50,82%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6759,12 +6759,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>236525</t>
+          <t>234252</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>291722</t>
+          <t>284797</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6774,12 +6774,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>34,38%</t>
+          <t>34,05%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>42,4%</t>
+          <t>41,39%</t>
         </is>
       </c>
     </row>
@@ -6802,12 +6802,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>305138</t>
+          <t>305077</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>351324</t>
+          <t>350996</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6817,12 +6817,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>58,47%</t>
+          <t>58,45%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>67,31%</t>
+          <t>67,25%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6837,12 +6837,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>83659</t>
+          <t>81701</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>110386</t>
+          <t>108907</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6852,12 +6852,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>50,36%</t>
+          <t>49,18%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>66,45%</t>
+          <t>65,56%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6872,12 +6872,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>396314</t>
+          <t>403239</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>451511</t>
+          <t>453784</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6887,12 +6887,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>57,6%</t>
+          <t>58,61%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>65,62%</t>
+          <t>65,95%</t>
         </is>
       </c>
     </row>
@@ -7032,12 +7032,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>412712</t>
+          <t>411465</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>478617</t>
+          <t>480920</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7047,12 +7047,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>35,9%</t>
+          <t>35,79%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>41,63%</t>
+          <t>41,83%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>323709</t>
+          <t>325419</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>380855</t>
+          <t>382436</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7082,12 +7082,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>39,2%</t>
+          <t>39,4%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>46,12%</t>
+          <t>46,31%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7102,12 +7102,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>749896</t>
+          <t>752041</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>840487</t>
+          <t>842475</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7117,12 +7117,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>37,96%</t>
+          <t>38,07%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>42,55%</t>
+          <t>42,65%</t>
         </is>
       </c>
     </row>
@@ -7145,12 +7145,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>671021</t>
+          <t>668718</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>736926</t>
+          <t>738173</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7160,12 +7160,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>58,37%</t>
+          <t>58,17%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>64,1%</t>
+          <t>64,21%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7180,12 +7180,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>445021</t>
+          <t>443440</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>502167</t>
+          <t>500457</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7195,12 +7195,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>53,88%</t>
+          <t>53,69%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>60,8%</t>
+          <t>60,6%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7215,12 +7215,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1135027</t>
+          <t>1133039</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1225618</t>
+          <t>1223473</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7230,12 +7230,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>57,45%</t>
+          <t>57,35%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>62,04%</t>
+          <t>61,93%</t>
         </is>
       </c>
     </row>
@@ -7375,12 +7375,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>229678</t>
+          <t>227717</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>279124</t>
+          <t>276729</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7390,12 +7390,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>37,0%</t>
+          <t>36,69%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>44,97%</t>
+          <t>44,58%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7410,12 +7410,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>326332</t>
+          <t>327016</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>380816</t>
+          <t>382989</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7425,12 +7425,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>44,2%</t>
+          <t>44,3%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>51,58%</t>
+          <t>51,88%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7445,12 +7445,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>569396</t>
+          <t>569362</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>644261</t>
+          <t>644676</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7465,7 +7465,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>47,41%</t>
+          <t>47,44%</t>
         </is>
       </c>
     </row>
@@ -7488,12 +7488,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>341582</t>
+          <t>343977</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>391028</t>
+          <t>392989</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7503,12 +7503,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>55,03%</t>
+          <t>55,42%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>63,0%</t>
+          <t>63,31%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7523,12 +7523,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>357428</t>
+          <t>355255</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>411912</t>
+          <t>411228</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7538,12 +7538,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>48,42%</t>
+          <t>48,12%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>55,8%</t>
+          <t>55,7%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7558,12 +7558,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>714689</t>
+          <t>714274</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>789554</t>
+          <t>789588</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7573,7 +7573,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>52,59%</t>
+          <t>52,56%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -7698,7 +7698,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -7718,12 +7718,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>37689</t>
+          <t>38794</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>65078</t>
+          <t>65046</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -7733,12 +7733,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>13,13%</t>
+          <t>13,51%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>22,66%</t>
+          <t>22,65%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -7753,12 +7753,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>482644</t>
+          <t>480818</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>551156</t>
+          <t>550144</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -7768,12 +7768,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>44,61%</t>
+          <t>44,44%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>50,94%</t>
+          <t>50,84%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -7788,12 +7788,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>525764</t>
+          <t>528759</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>605471</t>
+          <t>603720</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -7803,12 +7803,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>38,4%</t>
+          <t>38,62%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>44,22%</t>
+          <t>44,09%</t>
         </is>
       </c>
     </row>
@@ -7831,12 +7831,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>222067</t>
+          <t>222099</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>249456</t>
+          <t>248351</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -7846,12 +7846,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>77,34%</t>
+          <t>77,35%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>86,87%</t>
+          <t>86,49%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -7866,12 +7866,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>530869</t>
+          <t>531881</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>599381</t>
+          <t>601207</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7881,12 +7881,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>49,06%</t>
+          <t>49,16%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>55,39%</t>
+          <t>55,56%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7901,12 +7901,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>763699</t>
+          <t>765450</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>843406</t>
+          <t>840411</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7916,12 +7916,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>55,78%</t>
+          <t>55,91%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>61,6%</t>
+          <t>61,38%</t>
         </is>
       </c>
     </row>
@@ -8061,12 +8061,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>1086798</t>
+          <t>1087997</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>1202082</t>
+          <t>1201802</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8076,7 +8076,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>32,1%</t>
+          <t>32,13%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -8096,12 +8096,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>1442034</t>
+          <t>1451567</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>1565095</t>
+          <t>1572372</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8111,12 +8111,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>40,83%</t>
+          <t>41,1%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>44,32%</t>
+          <t>44,52%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8131,12 +8131,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>2564872</t>
+          <t>2570455</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>2737444</t>
+          <t>2735703</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8146,12 +8146,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>37,08%</t>
+          <t>37,16%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>39,57%</t>
+          <t>39,55%</t>
         </is>
       </c>
     </row>
@@ -8174,12 +8174,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>2183640</t>
+          <t>2183920</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>2298924</t>
+          <t>2297725</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8194,7 +8194,7 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>67,9%</t>
+          <t>67,87%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8209,12 +8209,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>1966501</t>
+          <t>1959224</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>2089562</t>
+          <t>2080029</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8224,12 +8224,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>55,68%</t>
+          <t>55,48%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>59,17%</t>
+          <t>58,9%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8244,12 +8244,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>4179874</t>
+          <t>4181615</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>4352446</t>
+          <t>4346863</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8259,12 +8259,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>60,43%</t>
+          <t>60,45%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>62,92%</t>
+          <t>62,84%</t>
         </is>
       </c>
     </row>
@@ -8633,32 +8633,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>136174</t>
+          <t>147240</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>115610</t>
+          <t>126027</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>156899</t>
+          <t>169718</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>27,09%</t>
+          <t>26,87%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>23,0%</t>
+          <t>22,99%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>31,21%</t>
+          <t>30,97%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8668,32 +8668,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>103807</t>
+          <t>114414</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>88230</t>
+          <t>99226</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>118907</t>
+          <t>131528</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>23,2%</t>
+          <t>23,43%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>19,72%</t>
+          <t>20,32%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>26,57%</t>
+          <t>26,93%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8703,32 +8703,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>239981</t>
+          <t>261654</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>218351</t>
+          <t>236078</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>268020</t>
+          <t>289991</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>25,26%</t>
+          <t>25,24%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>22,98%</t>
+          <t>22,78%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>28,21%</t>
+          <t>27,98%</t>
         </is>
       </c>
     </row>
@@ -8746,32 +8746,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>366493</t>
+          <t>400825</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>345768</t>
+          <t>378347</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>387057</t>
+          <t>422038</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>72,91%</t>
+          <t>73,13%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>68,79%</t>
+          <t>69,03%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>77,0%</t>
+          <t>77,01%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8781,32 +8781,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>343660</t>
+          <t>373997</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>328560</t>
+          <t>356883</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>359237</t>
+          <t>389185</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>76,8%</t>
+          <t>76,57%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>73,43%</t>
+          <t>73,07%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>80,28%</t>
+          <t>79,68%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8816,32 +8816,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>710153</t>
+          <t>774822</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>682114</t>
+          <t>746485</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>731783</t>
+          <t>800398</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>74,74%</t>
+          <t>74,76%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>71,79%</t>
+          <t>72,02%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>77,02%</t>
+          <t>77,22%</t>
         </is>
       </c>
     </row>
@@ -8859,17 +8859,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>502667</t>
+          <t>548065</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>502667</t>
+          <t>548065</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>502667</t>
+          <t>548065</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -8894,17 +8894,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>447467</t>
+          <t>488411</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>447467</t>
+          <t>488411</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>447467</t>
+          <t>488411</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -8929,17 +8929,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>950134</t>
+          <t>1036476</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>950134</t>
+          <t>1036476</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>950134</t>
+          <t>1036476</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -8976,32 +8976,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>115531</t>
+          <t>123521</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>96089</t>
+          <t>105087</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>135938</t>
+          <t>145045</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>25,55%</t>
+          <t>25,56%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>21,25%</t>
+          <t>21,75%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>30,06%</t>
+          <t>30,02%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -9011,67 +9011,67 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>125609</t>
+          <t>139356</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>110953</t>
+          <t>121429</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>141499</t>
+          <t>154428</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>32,83%</t>
+          <t>32,93%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
+          <t>28,7%</t>
+        </is>
+      </c>
+      <c r="P7" s="2" t="inlineStr">
+        <is>
+          <t>36,5%</t>
+        </is>
+      </c>
+      <c r="Q7" s="2" t="inlineStr">
+        <is>
+          <t>320</t>
+        </is>
+      </c>
+      <c r="R7" s="2" t="inlineStr">
+        <is>
+          <t>262876</t>
+        </is>
+      </c>
+      <c r="S7" s="2" t="inlineStr">
+        <is>
+          <t>235946</t>
+        </is>
+      </c>
+      <c r="T7" s="2" t="inlineStr">
+        <is>
+          <t>287431</t>
+        </is>
+      </c>
+      <c r="U7" s="2" t="inlineStr">
+        <is>
           <t>29,0%</t>
         </is>
       </c>
-      <c r="P7" s="2" t="inlineStr">
-        <is>
-          <t>36,99%</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>320</t>
-        </is>
-      </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t>241140</t>
-        </is>
-      </c>
-      <c r="S7" s="2" t="inlineStr">
-        <is>
-          <t>218861</t>
-        </is>
-      </c>
-      <c r="T7" s="2" t="inlineStr">
-        <is>
-          <t>265981</t>
-        </is>
-      </c>
-      <c r="U7" s="2" t="inlineStr">
-        <is>
-          <t>28,89%</t>
-        </is>
-      </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>26,22%</t>
+          <t>26,03%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>31,86%</t>
+          <t>31,71%</t>
         </is>
       </c>
     </row>
@@ -9089,32 +9089,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>336682</t>
+          <t>359691</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>316275</t>
+          <t>338167</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>356124</t>
+          <t>378125</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>74,45%</t>
+          <t>74,44%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>69,94%</t>
+          <t>69,98%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>78,75%</t>
+          <t>78,25%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -9124,67 +9124,67 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>256971</t>
+          <t>283787</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>241081</t>
+          <t>268715</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>271627</t>
+          <t>301714</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>67,17%</t>
+          <t>67,07%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>63,01%</t>
+          <t>63,5%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
+          <t>71,3%</t>
+        </is>
+      </c>
+      <c r="Q8" s="2" t="inlineStr">
+        <is>
+          <t>751</t>
+        </is>
+      </c>
+      <c r="R8" s="2" t="inlineStr">
+        <is>
+          <t>643479</t>
+        </is>
+      </c>
+      <c r="S8" s="2" t="inlineStr">
+        <is>
+          <t>618924</t>
+        </is>
+      </c>
+      <c r="T8" s="2" t="inlineStr">
+        <is>
+          <t>670409</t>
+        </is>
+      </c>
+      <c r="U8" s="2" t="inlineStr">
+        <is>
           <t>71,0%</t>
         </is>
       </c>
-      <c r="Q8" s="2" t="inlineStr">
-        <is>
-          <t>751</t>
-        </is>
-      </c>
-      <c r="R8" s="2" t="inlineStr">
-        <is>
-          <t>593653</t>
-        </is>
-      </c>
-      <c r="S8" s="2" t="inlineStr">
-        <is>
-          <t>568812</t>
-        </is>
-      </c>
-      <c r="T8" s="2" t="inlineStr">
-        <is>
-          <t>615932</t>
-        </is>
-      </c>
-      <c r="U8" s="2" t="inlineStr">
-        <is>
-          <t>71,11%</t>
-        </is>
-      </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>68,14%</t>
+          <t>68,29%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>73,78%</t>
+          <t>73,97%</t>
         </is>
       </c>
     </row>
@@ -9202,17 +9202,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>452213</t>
+          <t>483212</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>452213</t>
+          <t>483212</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>452213</t>
+          <t>483212</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -9237,17 +9237,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>382580</t>
+          <t>423143</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>382580</t>
+          <t>423143</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>382580</t>
+          <t>423143</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -9272,17 +9272,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>834793</t>
+          <t>906355</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>834793</t>
+          <t>906355</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>834793</t>
+          <t>906355</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -9319,32 +9319,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>158681</t>
+          <t>174466</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>61548</t>
+          <t>152587</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>261384</t>
+          <t>196094</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>23,78%</t>
+          <t>37,07%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>9,22%</t>
+          <t>32,42%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>39,17%</t>
+          <t>41,66%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -9354,32 +9354,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>67619</t>
+          <t>77889</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>57382</t>
+          <t>66971</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>77412</t>
+          <t>88859</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>40,55%</t>
+          <t>41,71%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>34,41%</t>
+          <t>35,86%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>46,42%</t>
+          <t>47,58%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -9389,32 +9389,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>226300</t>
+          <t>252355</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>83731</t>
+          <t>228827</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>329571</t>
+          <t>277436</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>27,13%</t>
+          <t>38,39%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>10,04%</t>
+          <t>34,81%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>39,52%</t>
+          <t>42,2%</t>
         </is>
       </c>
     </row>
@@ -9432,32 +9432,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>508593</t>
+          <t>296201</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>405890</t>
+          <t>274573</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>605726</t>
+          <t>318080</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>76,22%</t>
+          <t>62,93%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>60,83%</t>
+          <t>58,34%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>90,78%</t>
+          <t>67,58%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -9467,32 +9467,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>99130</t>
+          <t>108872</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>89337</t>
+          <t>97902</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>109367</t>
+          <t>119790</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>59,45%</t>
+          <t>58,29%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>53,58%</t>
+          <t>52,42%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>65,59%</t>
+          <t>64,14%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -9502,32 +9502,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>607722</t>
+          <t>405073</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>504451</t>
+          <t>379992</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>750291</t>
+          <t>428601</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>72,87%</t>
+          <t>61,61%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>60,48%</t>
+          <t>57,8%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>89,96%</t>
+          <t>65,19%</t>
         </is>
       </c>
     </row>
@@ -9545,17 +9545,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>667274</t>
+          <t>470667</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>667274</t>
+          <t>470667</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>667274</t>
+          <t>470667</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -9580,17 +9580,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>166749</t>
+          <t>186761</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>166749</t>
+          <t>186761</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>166749</t>
+          <t>186761</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -9615,17 +9615,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>834022</t>
+          <t>657428</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>834022</t>
+          <t>657428</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>834022</t>
+          <t>657428</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -9662,32 +9662,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>395419</t>
+          <t>427964</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>363758</t>
+          <t>398024</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>429817</t>
+          <t>462534</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>38,35%</t>
+          <t>37,95%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>35,28%</t>
+          <t>35,3%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>41,68%</t>
+          <t>41,02%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -9697,32 +9697,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>306863</t>
+          <t>348259</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>156345</t>
+          <t>320623</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>396440</t>
+          <t>372619</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>31,39%</t>
+          <t>40,49%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>15,99%</t>
+          <t>37,28%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>40,55%</t>
+          <t>43,32%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -9732,32 +9732,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>702282</t>
+          <t>776223</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>452640</t>
+          <t>732288</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>794756</t>
+          <t>816787</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>34,96%</t>
+          <t>39,05%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>22,53%</t>
+          <t>36,84%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>39,57%</t>
+          <t>41,09%</t>
         </is>
       </c>
     </row>
@@ -9775,32 +9775,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>635717</t>
+          <t>699724</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>601319</t>
+          <t>665154</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>667378</t>
+          <t>729664</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>61,65%</t>
+          <t>62,05%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>58,32%</t>
+          <t>58,98%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>64,72%</t>
+          <t>64,7%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9810,32 +9810,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>670693</t>
+          <t>511850</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>581116</t>
+          <t>487490</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>821211</t>
+          <t>539486</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>68,61%</t>
+          <t>59,51%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>59,45%</t>
+          <t>56,68%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>84,01%</t>
+          <t>62,72%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9845,32 +9845,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>1306410</t>
+          <t>1211575</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1213936</t>
+          <t>1171011</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1556052</t>
+          <t>1255510</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>65,04%</t>
+          <t>60,95%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>60,43%</t>
+          <t>58,91%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>77,47%</t>
+          <t>63,16%</t>
         </is>
       </c>
     </row>
@@ -9888,17 +9888,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1031136</t>
+          <t>1127688</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1031136</t>
+          <t>1127688</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>1031136</t>
+          <t>1127688</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -9923,17 +9923,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>977556</t>
+          <t>860109</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>977556</t>
+          <t>860109</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>977556</t>
+          <t>860109</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -9958,17 +9958,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>2008692</t>
+          <t>1987798</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>2008692</t>
+          <t>1987798</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>2008692</t>
+          <t>1987798</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -10005,32 +10005,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>203725</t>
+          <t>249972</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>181019</t>
+          <t>224301</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>227505</t>
+          <t>276738</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>43,07%</t>
+          <t>44,19%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>38,27%</t>
+          <t>39,65%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>48,1%</t>
+          <t>48,92%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -10040,32 +10040,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>378699</t>
+          <t>378714</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>286157</t>
+          <t>353681</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>432992</t>
+          <t>402923</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>45,24%</t>
+          <t>45,73%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>34,19%</t>
+          <t>42,71%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>51,73%</t>
+          <t>48,66%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -10075,32 +10075,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>582423</t>
+          <t>628686</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>486407</t>
+          <t>593082</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>638352</t>
+          <t>661724</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>44,46%</t>
+          <t>45,11%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>37,13%</t>
+          <t>42,55%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>48,73%</t>
+          <t>47,48%</t>
         </is>
       </c>
     </row>
@@ -10118,32 +10118,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>269268</t>
+          <t>315676</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>245488</t>
+          <t>288910</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>291974</t>
+          <t>341347</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>56,93%</t>
+          <t>55,81%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>51,9%</t>
+          <t>51,08%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>61,73%</t>
+          <t>60,35%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -10153,32 +10153,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>458370</t>
+          <t>449359</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>404077</t>
+          <t>425150</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>550912</t>
+          <t>474392</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>54,76%</t>
+          <t>54,27%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>48,27%</t>
+          <t>51,34%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>65,81%</t>
+          <t>57,29%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -10188,32 +10188,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>727638</t>
+          <t>765035</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>671709</t>
+          <t>731997</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>823654</t>
+          <t>800639</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>55,54%</t>
+          <t>54,89%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>51,27%</t>
+          <t>52,52%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>62,87%</t>
+          <t>57,45%</t>
         </is>
       </c>
     </row>
@@ -10231,17 +10231,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>472993</t>
+          <t>565648</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>472993</t>
+          <t>565648</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>472993</t>
+          <t>565648</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -10266,17 +10266,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>837069</t>
+          <t>828073</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>837069</t>
+          <t>828073</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>837069</t>
+          <t>828073</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -10301,17 +10301,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1310061</t>
+          <t>1393721</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1310061</t>
+          <t>1393721</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1310061</t>
+          <t>1393721</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -10333,7 +10333,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -10348,32 +10348,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>32184</t>
+          <t>28716</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>16830</t>
+          <t>15658</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>58535</t>
+          <t>51351</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>13,38%</t>
+          <t>12,1%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>7,0%</t>
+          <t>6,6%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>24,34%</t>
+          <t>21,65%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -10383,32 +10383,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>373544</t>
+          <t>410535</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>348819</t>
+          <t>381523</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>399139</t>
+          <t>438583</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>49,25%</t>
+          <t>48,82%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>45,99%</t>
+          <t>45,37%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>52,62%</t>
+          <t>52,16%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -10418,32 +10418,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>405728</t>
+          <t>439251</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>371097</t>
+          <t>406749</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>439279</t>
+          <t>474647</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>40,61%</t>
+          <t>40,74%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>37,15%</t>
+          <t>37,73%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>43,97%</t>
+          <t>44,03%</t>
         </is>
       </c>
     </row>
@@ -10461,32 +10461,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>208323</t>
+          <t>208512</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>181972</t>
+          <t>185877</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>223677</t>
+          <t>221570</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>86,62%</t>
+          <t>87,9%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>75,66%</t>
+          <t>78,35%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>93,0%</t>
+          <t>93,4%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -10496,32 +10496,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>384991</t>
+          <t>430319</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>359396</t>
+          <t>402271</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>409716</t>
+          <t>459331</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>50,75%</t>
+          <t>51,18%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>47,38%</t>
+          <t>47,84%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>54,01%</t>
+          <t>54,63%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -10531,32 +10531,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>593314</t>
+          <t>638831</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>559763</t>
+          <t>603435</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>627945</t>
+          <t>671333</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>59,39%</t>
+          <t>59,26%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>56,03%</t>
+          <t>55,97%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>62,85%</t>
+          <t>62,27%</t>
         </is>
       </c>
     </row>
@@ -10574,17 +10574,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>240507</t>
+          <t>237228</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>240507</t>
+          <t>237228</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>240507</t>
+          <t>237228</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -10609,17 +10609,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>758535</t>
+          <t>840854</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>758535</t>
+          <t>840854</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>758535</t>
+          <t>840854</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -10644,17 +10644,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>999042</t>
+          <t>1078082</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>999042</t>
+          <t>1078082</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>999042</t>
+          <t>1078082</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -10691,32 +10691,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>1041714</t>
+          <t>1151879</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>809885</t>
+          <t>1091387</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>1147027</t>
+          <t>1213379</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>30,94%</t>
+          <t>33,56%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>24,06%</t>
+          <t>31,8%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>34,07%</t>
+          <t>35,35%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10726,32 +10726,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>1356142</t>
+          <t>1469167</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>1117116</t>
+          <t>1418975</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>1481180</t>
+          <t>1527585</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>37,99%</t>
+          <t>40,5%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>31,29%</t>
+          <t>39,12%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>41,49%</t>
+          <t>42,11%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10761,32 +10761,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>2397856</t>
+          <t>2621046</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>2131689</t>
+          <t>2534899</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>2577856</t>
+          <t>2701409</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>34,57%</t>
+          <t>37,13%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>30,73%</t>
+          <t>35,91%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>37,16%</t>
+          <t>38,26%</t>
         </is>
       </c>
     </row>
@@ -10804,32 +10804,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>2325075</t>
+          <t>2280629</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>2219762</t>
+          <t>2219129</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>2556904</t>
+          <t>2341121</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>69,06%</t>
+          <t>66,44%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>65,93%</t>
+          <t>64,65%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>75,94%</t>
+          <t>68,2%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -10839,32 +10839,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>2213814</t>
+          <t>2158185</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>2088776</t>
+          <t>2099767</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>2452840</t>
+          <t>2208377</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>62,01%</t>
+          <t>59,5%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>58,51%</t>
+          <t>57,89%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>68,71%</t>
+          <t>60,88%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -10874,32 +10874,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>4538889</t>
+          <t>4438814</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>4358889</t>
+          <t>4358451</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>4805056</t>
+          <t>4524961</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>65,43%</t>
+          <t>62,87%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>62,84%</t>
+          <t>61,74%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>69,27%</t>
+          <t>64,09%</t>
         </is>
       </c>
     </row>
@@ -10917,17 +10917,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>3366789</t>
+          <t>3432508</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>3366789</t>
+          <t>3432508</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>3366789</t>
+          <t>3432508</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -10952,17 +10952,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>3569956</t>
+          <t>3627352</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>3569956</t>
+          <t>3627352</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>3569956</t>
+          <t>3627352</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -10987,17 +10987,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>6936745</t>
+          <t>7059860</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>6936745</t>
+          <t>7059860</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>6936745</t>
+          <t>7059860</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
